--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_12_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_12_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-18917.09153567202</v>
+        <v>-18914.1335385844</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23802671.2571657</v>
+        <v>23803645.71331563</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3157616.698101445</v>
+        <v>3157388.766134623</v>
       </c>
     </row>
     <row r="11">
@@ -22519,49 +22519,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G2" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H2" t="n">
-        <v>328.7292091509431</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I2" t="n">
-        <v>170.0248242437728</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J2" t="n">
-        <v>91.99244221512865</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K2" t="n">
-        <v>86.62179576859887</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L2" t="n">
-        <v>70.18749034687193</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M2" t="n">
-        <v>46.1077759408409</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N2" t="n">
-        <v>42.19343545588771</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O2" t="n">
-        <v>53.3120254920388</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P2" t="n">
-        <v>80.35007615727983</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q2" t="n">
-        <v>108.9989009297261</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R2" t="n">
-        <v>149.675824246293</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S2" t="n">
-        <v>185.1103710937831</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T2" t="n">
-        <v>218.502774187247</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U2" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -22598,22 +22598,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H3" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I3" t="n">
-        <v>80.19360641509437</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J3" t="n">
-        <v>73.79799459119508</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K3" t="n">
-        <v>47.18825972907612</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L3" t="n">
-        <v>16.65999298742156</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -22622,25 +22622,25 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>9.025801048218256</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P3" t="n">
-        <v>26.77235081055682</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q3" t="n">
-        <v>68.32003823696503</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R3" t="n">
-        <v>110.8236926432093</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S3" t="n">
-        <v>161.2554824245926</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T3" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V3" t="n">
         <v>232.8005871494253</v>
@@ -22677,49 +22677,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H4" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I4" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J4" t="n">
-        <v>93.72006078365847</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K4" t="n">
-        <v>74.3316188262732</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L4" t="n">
-        <v>64.91100415009086</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M4" t="n">
-        <v>65.148357718097</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N4" t="n">
-        <v>55.66238053080704</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O4" t="n">
-        <v>71.93148927151502</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P4" t="n">
-        <v>80.8043319180002</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q4" t="n">
-        <v>112.0940016294459</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R4" t="n">
-        <v>156.1309979345466</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S4" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T4" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U4" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V4" t="n">
         <v>252.137643323828</v>
@@ -22756,49 +22756,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>414.1851495754366</v>
+        <v>414.1825902111655</v>
       </c>
       <c r="H5" t="n">
-        <v>328.02930462833</v>
+        <v>328.0030935389889</v>
       </c>
       <c r="I5" t="n">
-        <v>167.3900805251798</v>
+        <v>167.2914106341195</v>
       </c>
       <c r="J5" t="n">
-        <v>86.19202512970136</v>
+        <v>85.97480228639998</v>
       </c>
       <c r="K5" t="n">
-        <v>77.92847416055847</v>
+        <v>77.60291342766286</v>
       </c>
       <c r="L5" t="n">
-        <v>59.40265617601742</v>
+        <v>58.99876929881117</v>
       </c>
       <c r="M5" t="n">
-        <v>34.10756991068988</v>
+        <v>33.65816793912805</v>
       </c>
       <c r="N5" t="n">
-        <v>29.9990535463397</v>
+        <v>29.54237978104271</v>
       </c>
       <c r="O5" t="n">
-        <v>41.7972164468124</v>
+        <v>41.36599235998582</v>
       </c>
       <c r="P5" t="n">
-        <v>70.52245304170174</v>
+        <v>70.15441326031711</v>
       </c>
       <c r="Q5" t="n">
-        <v>101.6187652513339</v>
+        <v>101.3423827029069</v>
       </c>
       <c r="R5" t="n">
-        <v>145.3828543970467</v>
+        <v>145.2220847311544</v>
       </c>
       <c r="S5" t="n">
-        <v>183.5530344103659</v>
+        <v>183.494712897039</v>
       </c>
       <c r="T5" t="n">
-        <v>218.2036083581012</v>
+        <v>218.1924047410046</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2562458726606</v>
+        <v>251.2560411235189</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,22 +22835,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.7455548990597</v>
+        <v>136.7441855184499</v>
       </c>
       <c r="H6" t="n">
-        <v>106.4603876327229</v>
+        <v>106.4471622989392</v>
       </c>
       <c r="I6" t="n">
-        <v>78.9346441509434</v>
+        <v>78.88749661679191</v>
       </c>
       <c r="J6" t="n">
-        <v>70.34330591194971</v>
+        <v>70.21392947460487</v>
       </c>
       <c r="K6" t="n">
-        <v>41.28364652152882</v>
+        <v>41.06252158333071</v>
       </c>
       <c r="L6" t="n">
-        <v>8.720511855345904</v>
+        <v>8.423182087426255</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -22859,25 +22859,25 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3258104821803158</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>19.78984137659441</v>
+        <v>19.5283497406852</v>
       </c>
       <c r="Q6" t="n">
-        <v>63.65241559545548</v>
+        <v>63.47761536183195</v>
       </c>
       <c r="R6" t="n">
-        <v>108.5533907564168</v>
+        <v>108.4683690375062</v>
       </c>
       <c r="S6" t="n">
-        <v>160.576284311385</v>
+        <v>160.5508486671644</v>
       </c>
       <c r="T6" t="n">
-        <v>197.7545211476518</v>
+        <v>197.7490015828257</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9020424583333</v>
+        <v>225.9019523675037</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,49 +22914,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.4896678830489</v>
+        <v>167.4885198403462</v>
       </c>
       <c r="H7" t="n">
-        <v>157.7700577533412</v>
+        <v>157.7598506100387</v>
       </c>
       <c r="I7" t="n">
-        <v>140.3746716485697</v>
+        <v>140.3401468734729</v>
       </c>
       <c r="J7" t="n">
-        <v>91.55270012792072</v>
+        <v>91.4715335088371</v>
       </c>
       <c r="K7" t="n">
-        <v>70.76997948201083</v>
+        <v>70.6365977934563</v>
       </c>
       <c r="L7" t="n">
-        <v>60.35333201894322</v>
+        <v>60.18264937930154</v>
       </c>
       <c r="M7" t="n">
-        <v>60.34293148858869</v>
+        <v>60.16297057655852</v>
       </c>
       <c r="N7" t="n">
-        <v>50.9712165963807</v>
+        <v>50.7955347526062</v>
       </c>
       <c r="O7" t="n">
-        <v>67.59844009118704</v>
+        <v>67.4361694735309</v>
       </c>
       <c r="P7" t="n">
-        <v>77.09665978685257</v>
+        <v>76.9578092403323</v>
       </c>
       <c r="Q7" t="n">
-        <v>109.5270016294459</v>
+        <v>109.4308687082193</v>
       </c>
       <c r="R7" t="n">
-        <v>154.7526044919236</v>
+        <v>154.7009843173077</v>
       </c>
       <c r="S7" t="n">
-        <v>215.2801062336936</v>
+        <v>215.2600989804104</v>
       </c>
       <c r="T7" t="n">
-        <v>225.8036222151667</v>
+        <v>225.7987169418005</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2916850941958</v>
+        <v>286.2916224736848</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,49 +22993,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>414.1127877663913</v>
+        <v>414.1100848867438</v>
       </c>
       <c r="H8" t="n">
-        <v>327.2882292514456</v>
+        <v>327.2605483852552</v>
       </c>
       <c r="I8" t="n">
-        <v>164.6003518819637</v>
+        <v>164.496149114352</v>
       </c>
       <c r="J8" t="n">
-        <v>80.05040703924922</v>
+        <v>79.82100350776379</v>
       </c>
       <c r="K8" t="n">
-        <v>68.72378069322195</v>
+        <v>68.37996426625614</v>
       </c>
       <c r="L8" t="n">
-        <v>47.98341999511311</v>
+        <v>47.55688531513388</v>
       </c>
       <c r="M8" t="n">
-        <v>21.40146940817755</v>
+        <v>20.92686739226636</v>
       </c>
       <c r="N8" t="n">
-        <v>17.08735505387762</v>
+        <v>16.60507348116786</v>
       </c>
       <c r="O8" t="n">
-        <v>29.60506569304377</v>
+        <v>29.14966087982927</v>
       </c>
       <c r="P8" t="n">
-        <v>60.11673444873711</v>
+        <v>59.72805697682125</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.80450394480141</v>
+        <v>93.51262335026308</v>
       </c>
       <c r="R8" t="n">
-        <v>140.8373569096096</v>
+        <v>140.6675721459498</v>
       </c>
       <c r="S8" t="n">
-        <v>181.9040896867479</v>
+        <v>181.8424978167795</v>
       </c>
       <c r="T8" t="n">
-        <v>217.8868445390057</v>
+        <v>217.8750126833486</v>
       </c>
       <c r="U8" t="n">
-        <v>251.250456927937</v>
+        <v>251.2502406975652</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,22 +23072,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.7068379179276</v>
+        <v>136.7053917498219</v>
       </c>
       <c r="H9" t="n">
-        <v>106.086463104421</v>
+        <v>106.0724961650838</v>
       </c>
       <c r="I9" t="n">
-        <v>77.60162528301889</v>
+        <v>77.55183396885138</v>
       </c>
       <c r="J9" t="n">
-        <v>66.68540025157242</v>
+        <v>66.54876907979121</v>
       </c>
       <c r="K9" t="n">
-        <v>35.03170312530251</v>
+        <v>34.79817869043559</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3140024213837762</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -23099,22 +23099,22 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>12.39659609357568</v>
+        <v>12.12044141380176</v>
       </c>
       <c r="Q9" t="n">
-        <v>58.7102269162103</v>
+        <v>58.52562482607891</v>
       </c>
       <c r="R9" t="n">
-        <v>106.1495416998131</v>
+        <v>106.0597524204047</v>
       </c>
       <c r="S9" t="n">
-        <v>159.8571333679888</v>
+        <v>159.8302714297086</v>
       </c>
       <c r="T9" t="n">
-        <v>197.5984645438782</v>
+        <v>197.5926354715572</v>
       </c>
       <c r="U9" t="n">
-        <v>225.899495288522</v>
+        <v>225.8994001458834</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,49 +23151,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.4572088666555</v>
+        <v>167.4559964478956</v>
       </c>
       <c r="H10" t="n">
-        <v>157.4814675894068</v>
+        <v>157.4706880844321</v>
       </c>
       <c r="I10" t="n">
-        <v>139.3985405010288</v>
+        <v>139.362079762321</v>
       </c>
       <c r="J10" t="n">
-        <v>89.25784766890436</v>
+        <v>89.17212966257721</v>
       </c>
       <c r="K10" t="n">
-        <v>66.99883194102728</v>
+        <v>66.85797092510069</v>
       </c>
       <c r="L10" t="n">
-        <v>55.52756152714002</v>
+        <v>55.34730792350439</v>
       </c>
       <c r="M10" t="n">
-        <v>55.25483312793305</v>
+        <v>55.06478097631943</v>
       </c>
       <c r="N10" t="n">
-        <v>46.00410184228244</v>
+        <v>45.81856870604673</v>
       </c>
       <c r="O10" t="n">
-        <v>63.01050566495762</v>
+        <v>62.83913578423567</v>
       </c>
       <c r="P10" t="n">
-        <v>73.17088929504938</v>
+        <v>73.02425275703001</v>
       </c>
       <c r="Q10" t="n">
-        <v>106.8090016294459</v>
+        <v>106.7074780912847</v>
       </c>
       <c r="R10" t="n">
-        <v>153.2931290820875</v>
+        <v>153.2386143258456</v>
       </c>
       <c r="S10" t="n">
-        <v>214.7144341025461</v>
+        <v>214.6933049501571</v>
       </c>
       <c r="T10" t="n">
-        <v>225.6649336905766</v>
+        <v>225.6597533558751</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2899146023925</v>
+        <v>286.2898484704602</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,49 +23230,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L11" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M11" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P11" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R11" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,19 +23309,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J12" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K12" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -23336,22 +23336,22 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R12" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S12" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,49 +23388,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K13" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L13" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M13" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N13" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O13" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P13" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R13" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,49 +23467,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K14" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L14" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M14" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P14" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R14" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,19 +23546,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J15" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K15" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -23573,22 +23573,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R15" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S15" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,49 +23625,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K16" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L16" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M16" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N16" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O16" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P16" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q16" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R16" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,49 +23704,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L17" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M17" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P17" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R17" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,19 +23783,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J18" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K18" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -23810,22 +23810,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R18" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S18" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,49 +23862,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K19" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L19" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M19" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N19" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O19" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P19" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q19" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R19" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,49 +23941,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K20" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L20" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M20" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P20" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R20" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,19 +24020,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J21" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K21" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -24047,22 +24047,22 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R21" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S21" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,49 +24099,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K22" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L22" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M22" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N22" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O22" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P22" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q22" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R22" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,49 +24178,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K23" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L23" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M23" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P23" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R23" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,19 +24257,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J24" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K24" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -24284,22 +24284,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R24" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S24" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,49 +24336,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K25" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L25" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M25" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N25" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O25" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P25" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q25" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R25" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,49 +24415,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K26" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L26" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M26" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P26" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R26" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,19 +24494,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J27" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K27" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -24521,22 +24521,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R27" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S27" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,49 +24573,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K28" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L28" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M28" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N28" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O28" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P28" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q28" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R28" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,49 +24652,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K29" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L29" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M29" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P29" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R29" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,19 +24731,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J30" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K30" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -24758,22 +24758,22 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R30" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S30" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,49 +24810,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K31" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L31" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M31" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N31" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O31" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P31" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q31" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R31" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,49 +24889,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K32" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L32" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M32" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P32" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R32" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,19 +24968,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J33" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K33" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -24995,22 +24995,22 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R33" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S33" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,49 +25047,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K34" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L34" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M34" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N34" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O34" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P34" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q34" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R34" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,49 +25126,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K35" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L35" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M35" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P35" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R35" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,19 +25205,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J36" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K36" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -25232,22 +25232,22 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R36" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S36" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,49 +25284,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K37" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L37" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M37" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N37" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O37" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P37" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q37" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R37" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,49 +25363,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K38" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L38" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M38" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>13.34886468801832</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P38" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.38548886942434</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R38" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,19 +25442,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J39" t="n">
-        <v>61.80819270440252</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K39" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -25469,22 +25469,22 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.538935716216997</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.12064201054979</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R39" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S39" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,49 +25521,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K40" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L40" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M40" t="n">
-        <v>48.47070198039194</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N40" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O40" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P40" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q40" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R40" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,49 +25600,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K41" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L41" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M41" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P41" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R41" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,19 +25679,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J42" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K42" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -25706,22 +25706,22 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R42" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S42" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,49 +25758,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K43" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L43" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M43" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N43" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O43" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P43" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q43" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R43" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,49 +25837,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
-        <v>71.86158291864604</v>
+        <v>71.92258334679384</v>
       </c>
       <c r="K44" t="n">
-        <v>56.45085607010611</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L44" t="n">
-        <v>32.75777175390675</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M44" t="n">
-        <v>4.460002071493761</v>
+        <v>4.586202945486122</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>13.3488646880183</v>
+        <v>13.46996085601006</v>
       </c>
       <c r="P44" t="n">
-        <v>46.24244299145039</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.38548886942431</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R44" t="n">
-        <v>134.7766935930266</v>
+        <v>134.8218408634681</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,19 +25916,19 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>75.82426679245282</v>
+        <v>75.83750674330534</v>
       </c>
       <c r="J45" t="n">
-        <v>61.8081927044025</v>
+        <v>61.84452414151258</v>
       </c>
       <c r="K45" t="n">
-        <v>26.69577859700046</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -25943,22 +25943,22 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.538935716216969</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.12064201054977</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R45" t="n">
-        <v>102.9444096243413</v>
+        <v>102.9682853879423</v>
       </c>
       <c r="S45" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,49 +25995,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>86.19804439021578</v>
+        <v>86.22083756629321</v>
       </c>
       <c r="K46" t="n">
-        <v>61.9706352197157</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M46" t="n">
-        <v>48.47070198039192</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N46" t="n">
-        <v>39.38128217015114</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O46" t="n">
-        <v>56.89325976331814</v>
+        <v>56.93882853040726</v>
       </c>
       <c r="P46" t="n">
-        <v>67.93652863931156</v>
+        <v>67.97552059180407</v>
       </c>
       <c r="Q46" t="n">
-        <v>103.1850016294458</v>
+        <v>103.2119976362414</v>
       </c>
       <c r="R46" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>234290.0405730429</v>
+        <v>234120.6119473168</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>248436.3116309123</v>
+        <v>248966.0827104822</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>262858.9893279758</v>
+        <v>263396.9483444988</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>281365.6479156295</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>281365.6479156296</v>
+        <v>281242.8786990619</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43681.19400514365</v>
+        <v>43649.60561729637</v>
       </c>
       <c r="C2" t="n">
-        <v>46318.63437186501</v>
+        <v>46417.40525110685</v>
       </c>
       <c r="D2" t="n">
-        <v>49007.60817979211</v>
+        <v>49107.90562355061</v>
       </c>
       <c r="E2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="F2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="G2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="H2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="I2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779123</v>
       </c>
       <c r="J2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779123</v>
       </c>
       <c r="K2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779122</v>
       </c>
       <c r="L2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="M2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="N2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="O2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
       <c r="P2" t="n">
-        <v>52458.00215376144</v>
+        <v>52435.11297779124</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>251502.9929999996</v>
+        <v>251306.7941829319</v>
       </c>
       <c r="C3" t="n">
-        <v>15480.23400000036</v>
+        <v>16245.3667340218</v>
       </c>
       <c r="D3" t="n">
-        <v>15415.45199999971</v>
+        <v>15446.02550868466</v>
       </c>
       <c r="E3" t="n">
-        <v>19281.67200000041</v>
+        <v>18597.87737763684</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39317.39999999999</v>
+        <v>39312.96135688073</v>
       </c>
       <c r="C5" t="n">
-        <v>39688</v>
+        <v>39701.87879260092</v>
       </c>
       <c r="D5" t="n">
-        <v>40080.39999999999</v>
+        <v>40095.05704060869</v>
       </c>
       <c r="E5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="F5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="G5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="H5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="I5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="J5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="K5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="L5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="M5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="N5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="O5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="P5" t="n">
-        <v>6976.000000000003</v>
+        <v>6972.102563257328</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-247139.1989948559</v>
+        <v>-246970.1499225162</v>
       </c>
       <c r="C6" t="n">
-        <v>-8849.599628135351</v>
+        <v>-9529.840275515875</v>
       </c>
       <c r="D6" t="n">
-        <v>-6488.243820207586</v>
+        <v>-6433.176925742744</v>
       </c>
       <c r="E6" t="n">
-        <v>26200.33015376104</v>
+        <v>26865.13303689707</v>
       </c>
       <c r="F6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="G6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="H6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="I6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.0104145339</v>
       </c>
       <c r="J6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.0104145339</v>
       </c>
       <c r="K6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453389</v>
       </c>
       <c r="L6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="M6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="N6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="O6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
       <c r="P6" t="n">
-        <v>45482.00215376144</v>
+        <v>45463.01041453391</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>260.9999999999995</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="C3" t="n">
-        <v>277.9999999999999</v>
+        <v>278.6366418624276</v>
       </c>
       <c r="D3" t="n">
-        <v>295.9999999999996</v>
+        <v>296.6723413123253</v>
       </c>
       <c r="E3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>320.0000000000001</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>17.84024934496279</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>18.03569944989766</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23.14887718571731</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.049246231155776</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7455929648241</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I2" t="n">
-        <v>40.45106532663311</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J2" t="n">
-        <v>89.05346231155764</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K2" t="n">
-        <v>133.4680552763817</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L2" t="n">
-        <v>165.5789246231153</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M2" t="n">
-        <v>184.2384572864318</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N2" t="n">
-        <v>187.2196281407032</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O2" t="n">
-        <v>176.7861859296479</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P2" t="n">
-        <v>150.8829195979897</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q2" t="n">
-        <v>113.3067889447234</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R2" t="n">
-        <v>65.90971356783909</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S2" t="n">
-        <v>23.90969849246228</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T2" t="n">
-        <v>4.593075376884413</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08393969849246209</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,22 +31038,22 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5613962264150935</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H3" t="n">
-        <v>5.42190566037735</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I3" t="n">
-        <v>19.32877358490563</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J3" t="n">
-        <v>53.03963207547162</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K3" t="n">
-        <v>90.65317924528287</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L3" t="n">
-        <v>121.8943867924526</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M3" t="n">
         <v>142.1340339220183</v>
@@ -31062,25 +31062,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>133.5704433962262</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P3" t="n">
-        <v>107.2020566037734</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q3" t="n">
-        <v>71.66173584905648</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R3" t="n">
-        <v>34.85581132075467</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S3" t="n">
-        <v>10.42768867924526</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T3" t="n">
-        <v>2.262820754716977</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0369339622641509</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4706557377049172</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H4" t="n">
-        <v>4.184557377049176</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I4" t="n">
-        <v>14.15390163934424</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J4" t="n">
-        <v>33.27536065573764</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K4" t="n">
-        <v>54.68163934426218</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L4" t="n">
-        <v>69.97367213114742</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M4" t="n">
-        <v>73.77742622950805</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N4" t="n">
-        <v>72.02316393442615</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O4" t="n">
-        <v>66.52504918032777</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P4" t="n">
-        <v>56.92367213114742</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.41099999999994</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R4" t="n">
-        <v>21.16239344262291</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S4" t="n">
-        <v>8.202245901639326</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T4" t="n">
-        <v>2.010983606557373</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02567213114754097</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.117587939698491</v>
+        <v>1.120147303969557</v>
       </c>
       <c r="H5" t="n">
-        <v>11.44549748743718</v>
+        <v>11.47170857677823</v>
       </c>
       <c r="I5" t="n">
-        <v>43.08580904522613</v>
+        <v>43.1844789362864</v>
       </c>
       <c r="J5" t="n">
-        <v>94.85387939698492</v>
+        <v>95.07110224028631</v>
       </c>
       <c r="K5" t="n">
-        <v>142.1613768844221</v>
+        <v>142.4869376173177</v>
       </c>
       <c r="L5" t="n">
-        <v>176.3637587939698</v>
+        <v>176.7676456711761</v>
       </c>
       <c r="M5" t="n">
-        <v>196.2386633165829</v>
+        <v>196.6880652881447</v>
       </c>
       <c r="N5" t="n">
-        <v>199.4140100502512</v>
+        <v>199.8706838155482</v>
       </c>
       <c r="O5" t="n">
-        <v>188.3009949748743</v>
+        <v>188.7322190617009</v>
       </c>
       <c r="P5" t="n">
-        <v>160.7105427135678</v>
+        <v>161.0785824949524</v>
       </c>
       <c r="Q5" t="n">
-        <v>120.6869246231155</v>
+        <v>120.9633071715426</v>
       </c>
       <c r="R5" t="n">
-        <v>70.20268341708542</v>
+        <v>70.36345308297777</v>
       </c>
       <c r="S5" t="n">
-        <v>25.4670351758794</v>
+        <v>25.52535668920632</v>
       </c>
       <c r="T5" t="n">
-        <v>4.892241206030149</v>
+        <v>4.90344482312674</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08940703517587929</v>
+        <v>0.08961178431756457</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,22 +31275,22 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5979622641509433</v>
+        <v>0.5993316447606933</v>
       </c>
       <c r="H6" t="n">
-        <v>5.775056603773585</v>
+        <v>5.788281937557223</v>
       </c>
       <c r="I6" t="n">
-        <v>20.5877358490566</v>
+        <v>20.63488338320808</v>
       </c>
       <c r="J6" t="n">
-        <v>56.49432075471698</v>
+        <v>56.62369719206183</v>
       </c>
       <c r="K6" t="n">
-        <v>96.55779245283017</v>
+        <v>96.77891739102829</v>
       </c>
       <c r="L6" t="n">
-        <v>129.8338679245283</v>
+        <v>130.1311976924479</v>
       </c>
       <c r="M6" t="n">
         <v>142.1340339220183</v>
@@ -31299,25 +31299,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>142.2704339622641</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>114.1845660377358</v>
+        <v>114.446057673645</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.32935849056604</v>
+        <v>76.50415872418957</v>
       </c>
       <c r="R6" t="n">
-        <v>37.12611320754718</v>
+        <v>37.2111349264578</v>
       </c>
       <c r="S6" t="n">
-        <v>11.10688679245282</v>
+        <v>11.1323224366734</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41020754716981</v>
+        <v>2.415727111995952</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03933962264150944</v>
+        <v>0.03942971347109826</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5013114754098359</v>
+        <v>0.5024595181125743</v>
       </c>
       <c r="H7" t="n">
-        <v>4.457114754098362</v>
+        <v>4.467321897400891</v>
       </c>
       <c r="I7" t="n">
-        <v>15.07580327868853</v>
+        <v>15.11032805378542</v>
       </c>
       <c r="J7" t="n">
-        <v>35.4427213114754</v>
+        <v>35.52388793055901</v>
       </c>
       <c r="K7" t="n">
-        <v>58.24327868852456</v>
+        <v>58.37666037707908</v>
       </c>
       <c r="L7" t="n">
-        <v>74.53134426229506</v>
+        <v>74.70202690193675</v>
       </c>
       <c r="M7" t="n">
-        <v>78.58285245901637</v>
+        <v>78.76281337104653</v>
       </c>
       <c r="N7" t="n">
-        <v>76.71432786885249</v>
+        <v>76.89000971262699</v>
       </c>
       <c r="O7" t="n">
-        <v>70.85809836065575</v>
+        <v>71.02036897831189</v>
       </c>
       <c r="P7" t="n">
-        <v>60.63134426229504</v>
+        <v>60.77019480881533</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.97799999999999</v>
+        <v>42.07413292122657</v>
       </c>
       <c r="R7" t="n">
-        <v>22.54078688524589</v>
+        <v>22.59240705986175</v>
       </c>
       <c r="S7" t="n">
-        <v>8.736491803278684</v>
+        <v>8.756499056561861</v>
       </c>
       <c r="T7" t="n">
-        <v>2.141967213114753</v>
+        <v>2.146872486480999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02734426229508199</v>
+        <v>0.02740688280614045</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.189949748743716</v>
+        <v>1.192652628391256</v>
       </c>
       <c r="H8" t="n">
-        <v>12.18657286432158</v>
+        <v>12.21425373051196</v>
       </c>
       <c r="I8" t="n">
-        <v>45.87553768844216</v>
+        <v>45.97974045605396</v>
       </c>
       <c r="J8" t="n">
-        <v>100.9954974874371</v>
+        <v>101.2249010189225</v>
       </c>
       <c r="K8" t="n">
-        <v>151.3660703517586</v>
+        <v>151.7098867787244</v>
       </c>
       <c r="L8" t="n">
-        <v>187.7829949748741</v>
+        <v>188.2095296548534</v>
       </c>
       <c r="M8" t="n">
-        <v>208.9447638190952</v>
+        <v>209.4193658350064</v>
       </c>
       <c r="N8" t="n">
-        <v>212.3257085427133</v>
+        <v>212.8079901154231</v>
       </c>
       <c r="O8" t="n">
-        <v>200.493145728643</v>
+        <v>200.9485505418575</v>
       </c>
       <c r="P8" t="n">
-        <v>171.1162613065324</v>
+        <v>171.5049387784483</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5011859296481</v>
+        <v>128.7930665241864</v>
       </c>
       <c r="R8" t="n">
-        <v>74.74818090452253</v>
+        <v>74.91796566818233</v>
       </c>
       <c r="S8" t="n">
-        <v>27.11597989949746</v>
+        <v>27.17757176946579</v>
       </c>
       <c r="T8" t="n">
-        <v>5.20900502512562</v>
+        <v>5.220836880782728</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09519597989949727</v>
+        <v>0.09541221027130049</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,22 +31512,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.636679245283018</v>
+        <v>0.6381254133887752</v>
       </c>
       <c r="H9" t="n">
-        <v>6.148981132075464</v>
+        <v>6.162948071412645</v>
       </c>
       <c r="I9" t="n">
-        <v>21.9207547169811</v>
+        <v>21.97054603114862</v>
       </c>
       <c r="J9" t="n">
-        <v>60.15222641509427</v>
+        <v>60.28885758687547</v>
       </c>
       <c r="K9" t="n">
-        <v>102.8097358490565</v>
+        <v>103.0432602839234</v>
       </c>
       <c r="L9" t="n">
-        <v>138.2403773584904</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
         <v>142.1340339220183</v>
@@ -31539,22 +31539,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>121.5778113207546</v>
+        <v>121.8539660005285</v>
       </c>
       <c r="Q9" t="n">
-        <v>81.27154716981121</v>
+        <v>81.45614925994261</v>
       </c>
       <c r="R9" t="n">
-        <v>39.5299622641509</v>
+        <v>39.61975154355923</v>
       </c>
       <c r="S9" t="n">
-        <v>11.82603773584903</v>
+        <v>11.85289967412921</v>
       </c>
       <c r="T9" t="n">
-        <v>2.566264150943392</v>
+        <v>2.572093223264404</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04188679245283015</v>
+        <v>0.0419819350913668</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.533770491803278</v>
+        <v>0.5349829105632095</v>
       </c>
       <c r="H10" t="n">
-        <v>4.745704918032783</v>
+        <v>4.756484423007447</v>
       </c>
       <c r="I10" t="n">
-        <v>16.05193442622949</v>
+        <v>16.08839516493725</v>
       </c>
       <c r="J10" t="n">
-        <v>37.73757377049175</v>
+        <v>37.82329177681891</v>
       </c>
       <c r="K10" t="n">
-        <v>62.0144262295081</v>
+        <v>62.15528724543469</v>
       </c>
       <c r="L10" t="n">
-        <v>79.35711475409826</v>
+        <v>79.5373683577339</v>
       </c>
       <c r="M10" t="n">
-        <v>83.670950819672</v>
+        <v>83.86100297128563</v>
       </c>
       <c r="N10" t="n">
-        <v>81.68144262295075</v>
+        <v>81.86697575918646</v>
       </c>
       <c r="O10" t="n">
-        <v>75.44603278688517</v>
+        <v>75.61740266760712</v>
       </c>
       <c r="P10" t="n">
-        <v>64.55711475409824</v>
+        <v>64.7037512921176</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.69599999999994</v>
+        <v>44.79752353816112</v>
       </c>
       <c r="R10" t="n">
-        <v>24.00026229508193</v>
+        <v>24.05477705132394</v>
       </c>
       <c r="S10" t="n">
-        <v>9.302163934426213</v>
+        <v>9.323293086815202</v>
       </c>
       <c r="T10" t="n">
-        <v>2.280655737704914</v>
+        <v>2.28583607240644</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02911475409836065</v>
+        <v>0.02918088603072055</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J11" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K11" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M11" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S11" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T11" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H12" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I12" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K12" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R12" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S12" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H13" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I13" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K13" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L13" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M13" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N13" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O13" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P13" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R13" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J14" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K14" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M14" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S14" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T14" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H15" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I15" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K15" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R15" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S15" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H16" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I16" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K16" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L16" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M16" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N16" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O16" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P16" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R16" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J17" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K17" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M17" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S17" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T17" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H18" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I18" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K18" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R18" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S18" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H19" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I19" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K19" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L19" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M19" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N19" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O19" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P19" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R19" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J20" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K20" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M20" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S20" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T20" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H21" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I21" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K21" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R21" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S21" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H22" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I22" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K22" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L22" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M22" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N22" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O22" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P22" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R22" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J23" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K23" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M23" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S23" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T23" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H24" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I24" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K24" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R24" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S24" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H25" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I25" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L25" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M25" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N25" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O25" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P25" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R25" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J26" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K26" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M26" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S26" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T26" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H27" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I27" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K27" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R27" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S27" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H28" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I28" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L28" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M28" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N28" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O28" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P28" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R28" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K29" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M29" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S29" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T29" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H30" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I30" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K30" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R30" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S30" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H31" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I31" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K31" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L31" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M31" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N31" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O31" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R31" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J32" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K32" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M32" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
-        <v>229.413063596591</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S32" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T32" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H33" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I33" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K33" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R33" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S33" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H34" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I34" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K34" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L34" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M34" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N34" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O34" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P34" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R34" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J35" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K35" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M35" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S35" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T35" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H36" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I36" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K36" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R36" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S36" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H37" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I37" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K37" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L37" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M37" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N37" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O37" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P37" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R37" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J38" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K38" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M38" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.80884422110556</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S38" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T38" t="n">
-        <v>5.631356783919598</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H39" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I39" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>65.02943396226418</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K39" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.86113207547173</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R39" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S39" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04528301886792456</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H40" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I40" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K40" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L40" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M40" t="n">
-        <v>90.45508196721312</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N40" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O40" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P40" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R40" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J41" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K41" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M41" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S41" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T41" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,19 +34119,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H42" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I42" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K42" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R42" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S42" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I43" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K43" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L43" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M43" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N43" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O43" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P43" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R43" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.28643216080402</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.59517587939701</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J44" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798924</v>
       </c>
       <c r="K44" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>203.0086432160805</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M44" t="n">
-        <v>225.886231155779</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.9905527638192</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.9202010050252</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.80884422110557</v>
+        <v>80.763696950664</v>
       </c>
       <c r="S44" t="n">
-        <v>29.31457286432163</v>
+        <v>29.2981950413031</v>
       </c>
       <c r="T44" t="n">
-        <v>5.631356783919599</v>
+        <v>5.628210588844949</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,19 +34356,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6883018867924531</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H45" t="n">
-        <v>6.647547169811324</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I45" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>65.02943396226419</v>
+        <v>64.99310252515411</v>
       </c>
       <c r="K45" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.4354716981133</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.86113207547174</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R45" t="n">
-        <v>42.73509433962268</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S45" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.774339622641509</v>
+        <v>2.772789620751896</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04528301886792457</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.577049180327869</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H46" t="n">
-        <v>5.130491803278693</v>
+        <v>5.127625437558784</v>
       </c>
       <c r="I46" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.79737704918033</v>
+        <v>40.7745838731029</v>
       </c>
       <c r="K46" t="n">
-        <v>67.04262295081968</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L46" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M46" t="n">
-        <v>90.45508196721313</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N46" t="n">
-        <v>88.30426229508205</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O46" t="n">
-        <v>81.56327868852465</v>
+        <v>81.51770992143553</v>
       </c>
       <c r="P46" t="n">
-        <v>69.79147540983605</v>
+        <v>69.75248345734354</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R46" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.465573770491803</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03147540983606562</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
